--- a/AAII_Financials/Quarterly/SMXT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SMXT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
   <si>
     <t>SMXT</t>
   </si>
@@ -2522,13 +2522,13 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>71000</v>
+        <v>69300</v>
       </c>
       <c r="E43" s="3">
         <v>61400</v>
       </c>
       <c r="F43" s="3">
-        <v>28300</v>
+        <v>26000</v>
       </c>
       <c r="G43" s="3">
         <v>8400</v>
@@ -2581,7 +2581,7 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1700</v>
+        <v>2700</v>
       </c>
       <c r="E44" s="3">
         <v>2300</v>
@@ -2645,8 +2645,8 @@
       <c r="E45" s="3">
         <v>2200</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
+      <c r="F45" s="3">
+        <v>2300</v>
       </c>
       <c r="G45" s="3">
         <v>2100</v>
@@ -3393,8 +3393,8 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>8</v>
+      <c r="D59" s="3">
+        <v>8600</v>
       </c>
       <c r="E59" s="3">
         <v>8600</v>
